--- a/data/trans_orig/imc_inf-Dificultad-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Dificultad-trans_orig.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
